--- a/Team-Data/2013-14/3-19-2013-14.xlsx
+++ b/Team-Data/2013-14/3-19-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -760,7 +827,7 @@
         <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
@@ -775,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -784,13 +851,13 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
@@ -811,7 +878,7 @@
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
         <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>0.333</v>
+        <v>0.324</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,46 +928,46 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>0.329</v>
+        <v>0.327</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0.772</v>
       </c>
       <c r="R3" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S3" t="n">
         <v>31.2</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.4</v>
       </c>
       <c r="W3" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X3" t="n">
         <v>4.4</v>
@@ -915,13 +982,13 @@
         <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -930,7 +997,7 @@
         <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
@@ -942,13 +1009,13 @@
         <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -966,19 +1033,19 @@
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
         <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.53</v>
+        <v>0.523</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1052,19 +1119,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
         <v>18.6</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.756</v>
+        <v>0.76</v>
       </c>
       <c r="R4" t="n">
         <v>8.800000000000001</v>
@@ -1079,13 +1146,13 @@
         <v>20.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
         <v>8.6</v>
       </c>
       <c r="X4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1</v>
@@ -1097,16 +1164,16 @@
         <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1154,25 +1221,25 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -1207,64 +1274,64 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
         <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>0.478</v>
+        <v>0.485</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O5" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0.734</v>
       </c>
       <c r="R5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
         <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
         <v>21.2</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X5" t="n">
         <v>5.2</v>
@@ -1273,25 +1340,25 @@
         <v>5.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
         <v>95.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF5" t="n">
         <v>17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1318,7 +1385,7 @@
         <v>20</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1327,16 +1394,16 @@
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1351,10 +1418,10 @@
         <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
         <v>26</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1407,7 +1474,7 @@
         <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.43</v>
@@ -1419,16 +1486,16 @@
         <v>17.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
         <v>11.8</v>
@@ -1437,7 +1504,7 @@
         <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U6" t="n">
         <v>22.4</v>
@@ -1446,7 +1513,7 @@
         <v>15.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>5.2</v>
@@ -1461,13 +1528,13 @@
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1503,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1521,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
         <v>24</v>
@@ -1676,7 +1743,7 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="n">
         <v>17</v>
@@ -1706,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.594</v>
+        <v>0.603</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
         <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O8" t="n">
         <v>17</v>
@@ -1792,22 +1859,22 @@
         <v>21.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="R8" t="n">
         <v>9.9</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T8" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W8" t="n">
         <v>8.699999999999999</v>
@@ -1825,31 +1892,31 @@
         <v>19.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.4</v>
+        <v>104.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1876,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT8" t="n">
         <v>27</v>
@@ -1897,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
         <v>21</v>
@@ -1906,7 +1973,7 @@
         <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.456</v>
+        <v>0.448</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J9" t="n">
         <v>85.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L9" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O9" t="n">
         <v>19</v>
@@ -1977,16 +2044,16 @@
         <v>0.72</v>
       </c>
       <c r="R9" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S9" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T9" t="n">
         <v>45.6</v>
       </c>
       <c r="U9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V9" t="n">
         <v>15.8</v>
@@ -2004,19 +2071,19 @@
         <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
         <v>19</v>
@@ -2034,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.448</v>
       </c>
       <c r="L10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M10" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="O10" t="n">
         <v>17.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q10" t="n">
         <v>0.671</v>
@@ -2168,13 +2235,13 @@
         <v>45</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
         <v>14.8</v>
       </c>
       <c r="W10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>5.2</v>
@@ -2189,13 +2256,13 @@
         <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC10" t="n">
         <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2216,13 +2283,13 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
       </c>
       <c r="AM10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
@@ -2255,13 +2322,13 @@
         <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2398,10 +2465,10 @@
         <v>6</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2416,7 +2483,7 @@
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -2431,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2583,16 +2650,16 @@
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2604,7 +2671,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.735</v>
+        <v>0.746</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,7 +2748,7 @@
         <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.454</v>
@@ -2693,7 +2760,7 @@
         <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
         <v>18.5</v>
@@ -2702,19 +2769,19 @@
         <v>23.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.782</v>
+        <v>0.784</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S13" t="n">
         <v>35.1</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U13" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V13" t="n">
         <v>15.3</v>
@@ -2732,19 +2799,19 @@
         <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
@@ -2762,16 +2829,16 @@
         <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>23</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2798,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2807,16 +2874,16 @@
         <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2968,10 +3035,10 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2983,7 +3050,7 @@
         <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
         <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,10 +3112,10 @@
         <v>37.7</v>
       </c>
       <c r="J15" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L15" t="n">
         <v>9.4</v>
@@ -3060,13 +3127,13 @@
         <v>0.382</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P15" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R15" t="n">
         <v>9.1</v>
@@ -3078,7 +3145,7 @@
         <v>41.4</v>
       </c>
       <c r="U15" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V15" t="n">
         <v>15.4</v>
@@ -3090,7 +3157,7 @@
         <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>20</v>
@@ -3099,40 +3166,40 @@
         <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG15" t="n">
         <v>25</v>
       </c>
-      <c r="AG15" t="n">
-        <v>26</v>
-      </c>
       <c r="AH15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN15" t="n">
         <v>3</v>
@@ -3144,10 +3211,10 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3159,10 +3226,10 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX15" t="n">
         <v>3</v>
@@ -3174,13 +3241,13 @@
         <v>9</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="n">
         <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>0.597</v>
+        <v>0.591</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3239,22 +3306,22 @@
         <v>14.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O16" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P16" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.751</v>
+        <v>0.748</v>
       </c>
       <c r="R16" t="n">
         <v>11.3</v>
       </c>
       <c r="S16" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T16" t="n">
         <v>42.2</v>
@@ -3266,7 +3333,7 @@
         <v>13.7</v>
       </c>
       <c r="W16" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X16" t="n">
         <v>4.7</v>
@@ -3278,16 +3345,16 @@
         <v>19.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3296,13 +3363,13 @@
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
         <v>23</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" t="n">
         <v>46</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.697</v>
+        <v>0.708</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,43 +3476,43 @@
         <v>39</v>
       </c>
       <c r="J17" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.506</v>
+        <v>0.507</v>
       </c>
       <c r="L17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O17" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>7.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
         <v>36.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>9.1</v>
@@ -3457,19 +3524,19 @@
         <v>3.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
         <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.9</v>
+        <v>104</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
@@ -3502,10 +3569,10 @@
         <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3529,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,22 +3736,22 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="n">
         <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3822,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.515</v>
+        <v>0.508</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J19" t="n">
         <v>87.59999999999999</v>
@@ -3782,25 +3849,25 @@
         <v>7.4</v>
       </c>
       <c r="M19" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="N19" t="n">
         <v>0.341</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.778</v>
       </c>
       <c r="R19" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T19" t="n">
         <v>45.1</v>
@@ -3824,16 +3891,16 @@
         <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.3</v>
+        <v>106.1</v>
       </c>
       <c r="AC19" t="n">
         <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3845,13 +3912,13 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3860,13 +3927,13 @@
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3878,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -3937,70 +4004,70 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
         <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>0.403</v>
+        <v>0.409</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
         <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>5.9</v>
       </c>
       <c r="M20" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O20" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
         <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
         <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X20" t="n">
         <v>6.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>22.8</v>
@@ -4012,31 +4079,31 @@
         <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>28</v>
@@ -4045,10 +4112,10 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
@@ -4057,16 +4124,16 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
         <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.412</v>
+        <v>0.403</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L21" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O21" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="P21" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.753</v>
+        <v>0.751</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
         <v>13</v>
@@ -4185,28 +4252,28 @@
         <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>7</v>
@@ -4215,19 +4282,19 @@
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4239,7 +4306,7 @@
         <v>18</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4257,16 +4324,16 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY21" t="n">
         <v>3</v>
       </c>
       <c r="AZ21" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA21" t="n">
         <v>26</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
         <v>3</v>
@@ -4406,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>14</v>
@@ -4445,7 +4512,7 @@
         <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
@@ -4454,7 +4521,7 @@
         <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>0.275</v>
+        <v>0.279</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J23" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q23" t="n">
         <v>0.767</v>
@@ -4528,7 +4595,7 @@
         <v>9.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
         <v>42.2</v>
@@ -4537,7 +4604,7 @@
         <v>21</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W23" t="n">
         <v>7.7</v>
@@ -4549,19 +4616,19 @@
         <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4576,7 +4643,7 @@
         <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>12</v>
@@ -4615,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4627,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>0.221</v>
+        <v>0.224</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
@@ -4683,28 +4750,28 @@
         <v>37.9</v>
       </c>
       <c r="J24" t="n">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.431</v>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M24" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.309</v>
+        <v>0.307</v>
       </c>
       <c r="O24" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P24" t="n">
         <v>23.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.711</v>
+        <v>0.714</v>
       </c>
       <c r="R24" t="n">
         <v>11.8</v>
@@ -4713,7 +4780,7 @@
         <v>31.6</v>
       </c>
       <c r="T24" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U24" t="n">
         <v>21.9</v>
@@ -4734,7 +4801,7 @@
         <v>22.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB24" t="n">
         <v>99.2</v>
@@ -4743,7 +4810,7 @@
         <v>-11.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
         <v>21</v>
@@ -4779,7 +4846,7 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4788,7 +4855,7 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
         <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.574</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
         <v>9.300000000000001</v>
@@ -4877,16 +4944,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O25" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P25" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
@@ -4907,7 +4974,7 @@
         <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
         <v>4.1</v>
@@ -4916,16 +4983,16 @@
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB25" t="n">
         <v>105.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4937,7 +5004,7 @@
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4955,22 +5022,22 @@
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="n">
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>14</v>
@@ -4985,10 +5052,10 @@
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>23</v>
@@ -4997,10 +5064,10 @@
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5122,10 +5189,10 @@
         <v>12</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
@@ -5140,7 +5207,7 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP26" t="n">
         <v>12</v>
@@ -5176,7 +5243,7 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5304,19 +5371,19 @@
         <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
       </c>
       <c r="AM27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN27" t="n">
         <v>27</v>
@@ -5346,10 +5413,10 @@
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.761</v>
+        <v>0.758</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="J28" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="O28" t="n">
         <v>15.9</v>
@@ -5438,19 +5505,19 @@
         <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
@@ -5459,19 +5526,19 @@
         <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA28" t="n">
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.4</v>
+        <v>105.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>18</v>
@@ -5516,16 +5583,16 @@
         <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
         <v>15</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>14</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
@@ -5537,13 +5604,13 @@
         <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" t="n">
         <v>29</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5593,10 +5660,10 @@
         <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L29" t="n">
         <v>8.4</v>
@@ -5605,25 +5672,25 @@
         <v>22.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O29" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U29" t="n">
         <v>21.4</v>
@@ -5644,16 +5711,16 @@
         <v>23.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.8</v>
+        <v>100.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5677,7 +5744,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5686,16 +5753,16 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS29" t="n">
         <v>19</v>
@@ -5722,10 +5789,10 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G30" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,7 +5842,7 @@
         <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K30" t="n">
         <v>0.443</v>
@@ -5787,16 +5854,16 @@
         <v>19.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O30" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P30" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R30" t="n">
         <v>10.9</v>
@@ -5805,19 +5872,19 @@
         <v>30.4</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
         <v>6.8</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
@@ -5829,22 +5896,22 @@
         <v>20.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="AC30" t="n">
         <v>-6.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF30" t="n">
         <v>26</v>
       </c>
-      <c r="AF30" t="n">
-        <v>27</v>
-      </c>
       <c r="AG30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
         <v>27</v>
@@ -5859,22 +5926,22 @@
         <v>23</v>
       </c>
       <c r="AL30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>24</v>
       </c>
       <c r="AN30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP30" t="n">
         <v>21</v>
       </c>
-      <c r="AO30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>22</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>23</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
@@ -5889,13 +5956,13 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5910,7 +5977,7 @@
         <v>29</v>
       </c>
       <c r="BC30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6041,7 +6108,7 @@
         <v>12</v>
       </c>
       <c r="AL31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM31" t="n">
         <v>17</v>
@@ -6077,7 +6144,7 @@
         <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6089,7 +6156,7 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-19-2013-14</t>
+          <t>2014-03-19</t>
         </is>
       </c>
     </row>
